--- a/tools/myCustomBlockly/製作積木教學/產生積木程式碼_Joystick.xlsx
+++ b/tools/myCustomBlockly/製作積木教學/產生積木程式碼_Joystick.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ArduinoSample\tools\myCustomBlockly\製作積木教學\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\Maker\ArduinoSample\tools\myCustomBlockly\製作積木教學\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9135" tabRatio="769" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9132" tabRatio="769" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="變數" sheetId="5" r:id="rId1"/>
@@ -17,12 +17,12 @@
     <sheet name="SETUP" sheetId="2" r:id="rId3"/>
     <sheet name="SETUP(1次會變動)" sheetId="7" r:id="rId4"/>
     <sheet name="FUNCTION" sheetId="4" r:id="rId5"/>
-    <sheet name="LOOP_dir" sheetId="3" r:id="rId6"/>
+    <sheet name="LOOP_isDir" sheetId="3" r:id="rId6"/>
     <sheet name="LOOP_sw" sheetId="10" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DEFINITION!$A$2:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">LOOP_dir!$C$1:$D$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">LOOP_isDir!$C$1:$D$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">LOOP_sw!$C$1:$D$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">SETUP!$A$2:$J$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'SETUP(1次會變動)'!$A$2:$G$3</definedName>
@@ -162,7 +162,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="61">
   <si>
     <t>DEFINITION區 連N拉N</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -294,8 +294,85 @@
     <t>', INPUT_PULLUP);\n '</t>
   </si>
   <si>
-    <r>
-      <t>''int joystick_xVal = analogRead('</t>
+    <t xml:space="preserve">''int joystick_xVal = analogRead(' </t>
+  </si>
+  <si>
+    <t xml:space="preserve">dropdown_ypin </t>
+  </si>
+  <si>
+    <t>');// vY腳位\n'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">''int joystick_yVal = analogRead(' </t>
+  </si>
+  <si>
+    <t xml:space="preserve">dropdown_xpin </t>
+  </si>
+  <si>
+    <t>');// vX腳位\n '</t>
+  </si>
+  <si>
+    <t>''int joystick_swVal = digitalRead('</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> value_swpin</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> '); \n '</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  String xDirect = "";</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  String yDirect = "";  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  if (joystick_xVal &lt; 480) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    xDirect="Left";</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  } else if (joystick_xVal &gt; 520) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    xDirect="Right";</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  }  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  if (joystick_yVal &lt; 480) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    yDirect ="Down";</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  } else if (joystick_yVal &gt; 520) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    yDirect ="Up";</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  return xDirect+yDirect;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  return !joystick_swVal;</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">''int joystick_xVal = analogRead(' </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFC55A11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>●</t>
     </r>
     <r>
       <rPr>
@@ -304,7 +381,204 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
+      <t>dropdown_ypin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFC55A11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFC55A11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>●</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFC55A11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>');// vY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFC55A11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>腳位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFC55A11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>\n'</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">''int joystick_yVal = analogRead(' </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFC55A11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>●</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>dropdown_xpin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFC55A11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFC55A11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>●</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFC55A11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>');// vX</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFC55A11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>腳位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFC55A11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>\n '</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>''int joystick_swVal = digitalRead('</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFC55A11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>●</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFC55A11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>value_swpin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFC55A11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>●</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFC55A11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> '); \n '</t>
+    </r>
+  </si>
+  <si>
+    <t>bool is_this_direct(String direct){</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  return direct == joystick_direct();</t>
+  </si>
+  <si>
+    <t>String joystick_direct(){</t>
+  </si>
+  <si>
+    <t>bool is_click_sw(){</t>
+  </si>
+  <si>
+    <t>''is_click_sw()'</t>
+  </si>
+  <si>
+    <r>
+      <t>''is_this_direct("'</t>
     </r>
     <r>
       <rPr>
@@ -324,7 +598,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">dropdown_ypin </t>
+      <t>dropdown_direct</t>
     </r>
     <r>
       <rPr>
@@ -340,22 +614,54 @@
     <r>
       <rPr>
         <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>'") '</t>
+    </r>
+  </si>
+  <si>
+    <t>''is_this_direct("'</t>
+  </si>
+  <si>
+    <t>'") '</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  joystick_xVal = analogRead('+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>dropdown_ypin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color rgb="FFC45911"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>');// vY</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFC45911"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>腳位</t>
+      <t xml:space="preserve"> +');</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  joystick_yVal = analogRead(' +</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>dropdown_xpin</t>
     </r>
     <r>
       <rPr>
@@ -364,12 +670,12 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>\n'</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>''int joystick_yVal = analogRead('</t>
+      <t xml:space="preserve"> +');</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  joystick_swVal = digitalRead('+ </t>
     </r>
     <r>
       <rPr>
@@ -378,27 +684,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>●</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>dropdown_xpin</t>
+      <t>value_swpin+</t>
     </r>
     <r>
       <rPr>
@@ -407,243 +693,8 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>●</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFC45911"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>');// vX</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFC45911"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>腳位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFC45911"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>\n '</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>''int joystick_swVal = digitalRead('</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>●</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> value_swpin</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>●</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFC45911"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> '); \n '</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">''int joystick_xVal = analogRead(' </t>
-  </si>
-  <si>
-    <t xml:space="preserve">dropdown_ypin </t>
-  </si>
-  <si>
-    <t>');// vY腳位\n'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">''int joystick_yVal = analogRead(' </t>
-  </si>
-  <si>
-    <t xml:space="preserve">dropdown_xpin </t>
-  </si>
-  <si>
-    <t>');// vX腳位\n '</t>
-  </si>
-  <si>
-    <t>''int joystick_swVal = digitalRead('</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> value_swpin</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> '); \n '</t>
-  </si>
-  <si>
-    <r>
-      <t>''is_this_direct(joystick_xVal,joystick_yVal,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>●</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>dropdown_direct</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>●</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>') '</t>
-    </r>
-  </si>
-  <si>
-    <t>''is_click_sw('joystick_swVal') '</t>
-  </si>
-  <si>
-    <t>''is_this_direct(joystick_xVal,joystick_yVal, '</t>
-  </si>
-  <si>
-    <t>') '</t>
-  </si>
-  <si>
-    <t>bool is_this_direct(int joystick_xVal,int joystick_yVal,String direct){</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  return direct == joystick_direct(joystick_xVal,joystick_yVal);</t>
-  </si>
-  <si>
-    <t>String joystick_direct(int joystick_xVal,int joystick_yVal){</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  String xDirect = "";</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  String yDirect = "";  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  if (joystick_xVal &lt; 480) {</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    xDirect="Left";</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  } else if (joystick_xVal &gt; 520) {</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    xDirect="Right";</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  }  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  if (joystick_yVal &lt; 480) {</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    yDirect ="Down";</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  } else if (joystick_yVal &gt; 520) {</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    yDirect ="Up";</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  return xDirect+yDirect;</t>
-  </si>
-  <si>
-    <t>bool is_click_sw(int joystick_swVal){</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  return !joystick_swVal;</t>
+      <t xml:space="preserve"> ');</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -764,17 +815,17 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FFC45911"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFC55A11"/>
       <name val="新細明體"/>
       <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -880,9 +931,6 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -931,7 +979,10 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1216,12 +1267,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="17.25" thickBot="1">
+    <row r="1" spans="1:2" ht="16.8" thickBot="1">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -1229,37 +1280,37 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="17.25" thickBot="1">
-      <c r="A2" s="19" t="s">
+    <row r="2" spans="1:2" ht="16.8" thickBot="1">
+      <c r="A2" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="17.25" thickBot="1">
-      <c r="A3" s="19" t="s">
+    <row r="3" spans="1:2" ht="16.8" thickBot="1">
+      <c r="A3" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="20" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="17.25" thickBot="1">
-      <c r="A4" s="19" t="s">
+    <row r="4" spans="1:2" ht="16.8" thickBot="1">
+      <c r="A4" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="20" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="17.25" thickBot="1">
-      <c r="B5" s="21" t="s">
+    <row r="5" spans="1:2" ht="16.8" thickBot="1">
+      <c r="B5" s="20" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="17.25" thickBot="1">
-      <c r="B6" s="20"/>
+    <row r="6" spans="1:2" ht="16.8" thickBot="1">
+      <c r="B6" s="19"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1271,12 +1322,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="1" width="62.75" customWidth="1"/>
-    <col min="2" max="2" width="13.375" customWidth="1"/>
-    <col min="3" max="3" width="10.125" customWidth="1"/>
-    <col min="4" max="4" width="32.75" customWidth="1"/>
+    <col min="1" max="1" width="62.77734375" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" customWidth="1"/>
+    <col min="4" max="4" width="32.77734375" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1287,20 +1338,20 @@
       <c r="B1" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="9" t="str">
+      <c r="C1" s="8" t="str">
         <f>"Blockly.Arduino.definitions_['"&amp;C2&amp;"'] = '"&amp;C3&amp;"';"</f>
         <v>Blockly.Arduino.definitions_['amani_joystick_init'] = '';</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="8" t="str">
+      <c r="E1" s="7" t="str">
         <f>"Blockly.Arduino.definitions_['"&amp;變數!A2&amp;"'] = "&amp;DEFINITION!E3&amp;E5&amp;E7&amp;";"</f>
         <v>Blockly.Arduino.definitions_['amani_joystick_init'] = ''int joystick_xVal = analogRead(' +dropdown_ypin +');// vY腳位\n'+++++++++++''int joystick_yVal = analogRead(' +dropdown_xpin +');// vX腳位\n '+++++''int joystick_swVal = digitalRead('+ value_swpin+ '); \n '+++++;</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="16"/>
+      <c r="A2" s="15"/>
       <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
@@ -1309,20 +1360,20 @@
         <v>amani_joystick_init</v>
       </c>
       <c r="D2" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" t="s">
         <v>25</v>
       </c>
-      <c r="E2" t="s">
-        <v>28</v>
-      </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="16"/>
+      <c r="A3" s="15"/>
       <c r="B3" s="5" t="s">
         <v>8</v>
       </c>
@@ -1339,7 +1390,7 @@
  IF(NOT(ISBLANK(A11)),A11&amp;"\n","")</f>
         <v/>
       </c>
-      <c r="E3" s="7" t="str">
+      <c r="E3" s="6" t="str">
         <f>E2&amp;"+"&amp;F2&amp;"+"&amp;G2&amp;"+"&amp;H2&amp;"+"&amp;I2&amp;"+"&amp;J2&amp;"+"&amp;K2&amp;"+"&amp;L2&amp;"+"&amp;M2&amp;"+"&amp;N2&amp;"+"&amp;O2&amp;"+"&amp;P2&amp;"+"&amp;Q2&amp;"+"&amp;R2</f>
         <v>''int joystick_xVal = analogRead(' +dropdown_ypin +');// vY腳位\n'+++++++++++</v>
       </c>
@@ -1347,21 +1398,21 @@
     <row r="4" spans="1:7">
       <c r="A4" s="3"/>
       <c r="D4" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>31</v>
+        <v>48</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>28</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="3"/>
-      <c r="E5" s="7" t="str">
+      <c r="E5" s="6" t="str">
         <f>E4&amp;"+"&amp;F4&amp;"+"&amp;G4&amp;"+"&amp;H4&amp;"+"&amp;I4&amp;"+"&amp;J4&amp;"+"&amp;K4&amp;"+"&amp;L4</f>
         <v>''int joystick_yVal = analogRead(' +dropdown_xpin +');// vX腳位\n '+++++</v>
       </c>
@@ -1369,21 +1420,21 @@
     <row r="6" spans="1:7">
       <c r="A6" s="3"/>
       <c r="D6" s="16" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="3"/>
-      <c r="E7" s="7" t="str">
+      <c r="E7" s="6" t="str">
         <f>E6&amp;"+"&amp;F6&amp;"+"&amp;G6&amp;"+"&amp;H6&amp;"+"&amp;I6&amp;"+"&amp;J6&amp;"+"&amp;K6&amp;"+"&amp;L6</f>
         <v>''int joystick_swVal = digitalRead('+ value_swpin+ '); \n '+++++</v>
       </c>
@@ -1394,7 +1445,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="3"/>
-      <c r="E9" s="7" t="str">
+      <c r="E9" s="6" t="str">
         <f>E8&amp;"+"&amp;F8&amp;"+"&amp;G8&amp;"+"&amp;H8&amp;"+"&amp;I8&amp;"+"&amp;J8&amp;"+"&amp;K8&amp;"+"&amp;L8</f>
         <v>+++++++</v>
       </c>
@@ -1405,7 +1456,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="3"/>
-      <c r="E11" s="7" t="str">
+      <c r="E11" s="6" t="str">
         <f>E10&amp;"+"&amp;F10&amp;"+"&amp;G10&amp;"+"&amp;H10&amp;"+"&amp;I10&amp;"+"&amp;J10&amp;"+"&amp;K10&amp;"+"&amp;L10</f>
         <v>+++++++</v>
       </c>
@@ -1421,12 +1472,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="1" width="64.5" customWidth="1"/>
-    <col min="2" max="2" width="11.375" customWidth="1"/>
-    <col min="4" max="4" width="32.875" customWidth="1"/>
-    <col min="5" max="5" width="26.25" customWidth="1"/>
+    <col min="1" max="1" width="64.44140625" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" customWidth="1"/>
+    <col min="4" max="4" width="32.88671875" customWidth="1"/>
+    <col min="5" max="5" width="26.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1436,14 +1487,14 @@
       <c r="B1" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="9" t="str">
+      <c r="C1" s="8" t="str">
         <f>"Blockly.Arduino.setups_['"&amp;C2&amp;"'] = '"&amp;C3&amp;"';"</f>
         <v>Blockly.Arduino.setups_['amani_joystick_init'] = '';</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="8" t="str">
+      <c r="E1" s="7" t="str">
         <f>"Blockly.Arduino.setups_['"&amp;
 變數!$A$2 &amp;"' + "&amp;
 變數!B2 &amp;" + "&amp;
@@ -1455,7 +1506,7 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="16"/>
+      <c r="A2" s="15"/>
       <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
@@ -1463,11 +1514,11 @@
         <f>變數!$A$2</f>
         <v>amani_joystick_init</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="12"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="11"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="17"/>
+      <c r="A3" s="16"/>
       <c r="B3" s="5" t="s">
         <v>8</v>
       </c>
@@ -1484,98 +1535,98 @@
  IF(NOT(ISBLANK(A11)),A11&amp;"\n","")</f>
         <v/>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="13" t="str">
+      <c r="D3" s="9"/>
+      <c r="E3" s="12" t="str">
         <f>E2&amp;"+"&amp;F2&amp;"+"&amp;G2&amp;"+"&amp;H2&amp;"+"&amp;I2&amp;"+"&amp;J2&amp;"+"&amp;K2&amp;"+"&amp;L2</f>
         <v>+++++++</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="D4" s="1"/>
-      <c r="E4" s="14"/>
+      <c r="E4" s="13"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="D5" s="10"/>
-      <c r="E5" s="13" t="str">
+      <c r="D5" s="9"/>
+      <c r="E5" s="12" t="str">
         <f>E4&amp;"+"&amp;F4&amp;"+"&amp;G4&amp;"+"&amp;H4&amp;"+"&amp;I4&amp;"+"&amp;J4&amp;"+"&amp;K4&amp;"+"&amp;L4</f>
         <v>+++++++</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="D6" s="11"/>
-      <c r="E6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="9"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="D7" s="10"/>
-      <c r="E7" s="13" t="str">
+      <c r="D7" s="9"/>
+      <c r="E7" s="12" t="str">
         <f>E6&amp;"+"&amp;F6&amp;"+"&amp;G6&amp;"+"&amp;H6&amp;"+"&amp;I6&amp;"+"&amp;J6&amp;"+"&amp;K6&amp;"+"&amp;L6</f>
         <v>+++++++</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="D8" s="11"/>
-      <c r="E8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="9"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="D9" s="10"/>
-      <c r="E9" s="13" t="str">
+      <c r="D9" s="9"/>
+      <c r="E9" s="12" t="str">
         <f>E8&amp;"+"&amp;F8&amp;"+"&amp;G8&amp;"+"&amp;H8&amp;"+"&amp;I8&amp;"+"&amp;J8&amp;"+"&amp;K8&amp;"+"&amp;L8</f>
         <v>+++++++</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="D10" s="11"/>
-      <c r="E10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="9"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="D11" s="10"/>
-      <c r="E11" s="13" t="str">
+      <c r="D11" s="9"/>
+      <c r="E11" s="12" t="str">
         <f>E10&amp;"+"&amp;F10&amp;"+"&amp;G10&amp;"+"&amp;H10&amp;"+"&amp;I10&amp;"+"&amp;J10&amp;"+"&amp;K10&amp;"+"&amp;L10</f>
         <v>+++++++</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
     </row>
     <row r="17" spans="4:5">
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
     </row>
     <row r="18" spans="4:5">
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
     </row>
     <row r="19" spans="4:5">
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
     </row>
     <row r="20" spans="4:5">
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
     </row>
     <row r="21" spans="4:5">
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
     </row>
     <row r="22" spans="4:5">
-      <c r="D22" s="10"/>
+      <c r="D22" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1588,17 +1639,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="1" width="32.875" customWidth="1"/>
-    <col min="2" max="2" width="26.25" customWidth="1"/>
+    <col min="1" max="1" width="32.88671875" customWidth="1"/>
+    <col min="2" max="2" width="26.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="8" t="str">
+      <c r="B1" s="7" t="str">
         <f>"Blockly.Arduino.setups_['"&amp;變數!$A$2&amp;"'] = "&amp;
 'SETUP(1次會變動)'!B3 &amp; 'SETUP(1次會變動)'!B5
 &amp;";"</f>
@@ -1606,10 +1657,10 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
@@ -1620,98 +1671,98 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="10"/>
-      <c r="B3" s="13" t="str">
+      <c r="A3" s="9"/>
+      <c r="B3" s="12" t="str">
         <f>B2&amp;"+"&amp;C2&amp;"+"&amp;D2&amp;"+"&amp;E2&amp;"+"&amp;F2&amp;"+"&amp;G2&amp;"+"&amp;H2&amp;"+"&amp;I2</f>
         <v>''pinMode('+value_swpin+', INPUT_PULLUP);\n '+++++</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="22"/>
-      <c r="B4" s="14"/>
+      <c r="A4" s="21"/>
+      <c r="B4" s="13"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="10"/>
-      <c r="B5" s="13" t="str">
+      <c r="A5" s="9"/>
+      <c r="B5" s="12" t="str">
         <f>B4&amp;"+"&amp;C4&amp;"+"&amp;D4&amp;"+"&amp;E4&amp;"+"&amp;F4&amp;"+"&amp;G4&amp;"+"&amp;H4&amp;"+"&amp;I4</f>
         <v>+++++++</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="11"/>
-      <c r="B6" s="10"/>
+      <c r="A6" s="10"/>
+      <c r="B6" s="9"/>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="10"/>
-      <c r="B7" s="13" t="str">
+      <c r="A7" s="9"/>
+      <c r="B7" s="12" t="str">
         <f>B6&amp;"+"&amp;C6&amp;"+"&amp;D6&amp;"+"&amp;E6&amp;"+"&amp;F6&amp;"+"&amp;G6&amp;"+"&amp;H6&amp;"+"&amp;I6</f>
         <v>+++++++</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="11"/>
-      <c r="B8" s="10"/>
+      <c r="A8" s="10"/>
+      <c r="B8" s="9"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="10"/>
-      <c r="B9" s="13" t="str">
+      <c r="A9" s="9"/>
+      <c r="B9" s="12" t="str">
         <f>B8&amp;"+"&amp;C8&amp;"+"&amp;D8&amp;"+"&amp;E8&amp;"+"&amp;F8&amp;"+"&amp;G8&amp;"+"&amp;H8&amp;"+"&amp;I8</f>
         <v>+++++++</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="11"/>
-      <c r="B10" s="10"/>
+      <c r="A10" s="10"/>
+      <c r="B10" s="9"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="10"/>
-      <c r="B11" s="13" t="str">
+      <c r="A11" s="9"/>
+      <c r="B11" s="12" t="str">
         <f>B10&amp;"+"&amp;C10&amp;"+"&amp;D10&amp;"+"&amp;E10&amp;"+"&amp;F10&amp;"+"&amp;G10&amp;"+"&amp;H10&amp;"+"&amp;I10</f>
         <v>+++++++</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="10"/>
+      <c r="A22" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1723,10 +1774,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="1" width="64.25" customWidth="1"/>
+    <col min="1" max="1" width="64.21875" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1736,17 +1788,17 @@
       <c r="B1" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="9" t="str">
+      <c r="C1" s="8" t="str">
         <f>"Blockly.Arduino.functions_['"&amp;C2&amp;"'] = '"&amp;C3&amp;"';"</f>
-        <v>Blockly.Arduino.functions_['amani_joystick_init'] = 'bool is_this_direct(int joystick_xVal,int joystick_yVal,String direct){\n  return direct == joystick_direct(joystick_xVal,joystick_yVal);\n}\nString joystick_direct(int joystick_xVal,int joystick_yVal){\n  String xDirect = "";\n  String yDirect = "";  \n  if (joystick_xVal &lt; 480) {\n    xDirect="Left";\n  } else if (joystick_xVal &gt; 520) {\n    xDirect="Right";\n  }  \n  if (joystick_yVal &lt; 480) {\n    yDirect ="Down";\n  } else if (joystick_yVal &gt; 520) {\n    yDirect ="Up";\n  }\n  return xDirect+yDirect;\n}\nbool is_click_sw(int joystick_swVal){\n  return !joystick_swVal;\n}\n';</v>
+        <v>Blockly.Arduino.functions_['amani_joystick_init'] = 'bool is_this_direct(String direct){\n  return direct == joystick_direct();\n}\nString joystick_direct(){\n  joystick_xVal = analogRead('+dropdown_ypin +');\n  joystick_yVal = analogRead(' +dropdown_xpin +');\n  String xDirect = "";\n  String yDirect = "";  \n  if (joystick_xVal &lt; 480) {\n    xDirect="Left";\n  } else if (joystick_xVal &gt; 520) {\n    xDirect="Right";\n  }  \n  if (joystick_yVal &lt; 480) {\n    yDirect ="Down";\n  } else if (joystick_yVal &gt; 520) {\n    yDirect ="Up";\n  }\n  return xDirect+yDirect;\n}\nbool is_click_sw(){\n  joystick_swVal = digitalRead('+ value_swpin+ ');\n  return !joystick_swVal;\n}\n';</v>
       </c>
       <c r="D1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="16" t="s">
-        <v>41</v>
+      <c r="A2" s="15" t="s">
+        <v>50</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>9</v>
@@ -1757,8 +1809,8 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="16" t="s">
-        <v>42</v>
+      <c r="A3" s="15" t="s">
+        <v>51</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>8</v>
@@ -1788,101 +1840,116 @@
  IF(NOT(ISBLANK(A23)),A23&amp;"\n","")&amp;
  IF(NOT(ISBLANK(A24)),A24&amp;"\n","")&amp;
  IF(NOT(ISBLANK(A25)),A25&amp;"\n","")</f>
-        <v>bool is_this_direct(int joystick_xVal,int joystick_yVal,String direct){\n  return direct == joystick_direct(joystick_xVal,joystick_yVal);\n}\nString joystick_direct(int joystick_xVal,int joystick_yVal){\n  String xDirect = "";\n  String yDirect = "";  \n  if (joystick_xVal &lt; 480) {\n    xDirect="Left";\n  } else if (joystick_xVal &gt; 520) {\n    xDirect="Right";\n  }  \n  if (joystick_yVal &lt; 480) {\n    yDirect ="Down";\n  } else if (joystick_yVal &gt; 520) {\n    yDirect ="Up";\n  }\n  return xDirect+yDirect;\n}\nbool is_click_sw(int joystick_swVal){\n  return !joystick_swVal;\n}\n</v>
+        <v>bool is_this_direct(String direct){\n  return direct == joystick_direct();\n}\nString joystick_direct(){\n  joystick_xVal = analogRead('+dropdown_ypin +');\n  joystick_yVal = analogRead(' +dropdown_xpin +');\n  String xDirect = "";\n  String yDirect = "";  \n  if (joystick_xVal &lt; 480) {\n    xDirect="Left";\n  } else if (joystick_xVal &gt; 520) {\n    xDirect="Right";\n  }  \n  if (joystick_yVal &lt; 480) {\n    yDirect ="Down";\n  } else if (joystick_yVal &gt; 520) {\n    yDirect ="Up";\n  }\n  return xDirect+yDirect;\n}\nbool is_click_sw(){\n  joystick_swVal = digitalRead('+ value_swpin+ ');\n  return !joystick_swVal;\n}\n</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="15" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="16" t="s">
+    <row r="18" spans="1:1">
+      <c r="A18" s="15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="16" t="s">
+    <row r="19" spans="1:1">
+      <c r="A19" s="15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="15" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="16" t="s">
+    <row r="21" spans="1:1">
+      <c r="A21" s="15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="15" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="16" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="16" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="16" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="16" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="16" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="16" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="16" t="s">
+    <row r="25" spans="1:1">
+      <c r="A25" s="15" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1896,9 +1963,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="C1:L14"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="1" width="23.625" customWidth="1"/>
+    <col min="1" max="1" width="23.6640625" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
   </cols>
@@ -1907,88 +1974,88 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="str">
+      <c r="D1" s="7" t="str">
         <f>"var code ="&amp;D3&amp;";"</f>
-        <v>var code =''is_this_direct(joystick_xVal,joystick_yVal, '+dropdown_direct+') '+++++;</v>
+        <v>var code =''is_this_direct("'+dropdown_direct+'") '+++++;</v>
       </c>
     </row>
     <row r="2" spans="3:12">
-      <c r="C2" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>39</v>
+      <c r="C2" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
-      </c>
-      <c r="L2" s="18"/>
+        <v>57</v>
+      </c>
+      <c r="L2" s="17"/>
     </row>
     <row r="3" spans="3:12">
-      <c r="C3" s="10"/>
-      <c r="D3" s="13" t="str">
+      <c r="C3" s="9"/>
+      <c r="D3" s="12" t="str">
         <f>D2&amp;"+"&amp;E2&amp;"+"&amp;F2&amp;"+"&amp;G2&amp;"+"&amp;H2&amp;"+"&amp;I2&amp;"+"&amp;J2&amp;"+"&amp;K2</f>
-        <v>''is_this_direct(joystick_xVal,joystick_yVal, '+dropdown_direct+') '+++++</v>
+        <v>''is_this_direct("'+dropdown_direct+'") '+++++</v>
       </c>
     </row>
     <row r="4" spans="3:12">
       <c r="C4" s="1"/>
-      <c r="D4" s="14"/>
+      <c r="D4" s="13"/>
     </row>
     <row r="5" spans="3:12">
-      <c r="C5" s="10"/>
-      <c r="D5" s="13" t="str">
+      <c r="C5" s="9"/>
+      <c r="D5" s="12" t="str">
         <f>D4&amp;"+"&amp;E4&amp;"+"&amp;F4&amp;"+"&amp;G4&amp;"+"&amp;H4&amp;"+"&amp;I4&amp;"+"&amp;J4&amp;"+"&amp;K4</f>
         <v>+++++++</v>
       </c>
     </row>
     <row r="6" spans="3:12">
-      <c r="C6" s="11"/>
-      <c r="D6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="9"/>
     </row>
     <row r="7" spans="3:12">
-      <c r="C7" s="10"/>
-      <c r="D7" s="13" t="str">
+      <c r="C7" s="9"/>
+      <c r="D7" s="12" t="str">
         <f>D6&amp;"+"&amp;E6&amp;"+"&amp;F6&amp;"+"&amp;G6&amp;"+"&amp;H6&amp;"+"&amp;I6&amp;"+"&amp;J6&amp;"+"&amp;K6</f>
         <v>+++++++</v>
       </c>
     </row>
     <row r="8" spans="3:12">
-      <c r="C8" s="11"/>
-      <c r="D8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="9"/>
     </row>
     <row r="9" spans="3:12">
-      <c r="C9" s="10"/>
-      <c r="D9" s="13" t="str">
+      <c r="C9" s="9"/>
+      <c r="D9" s="12" t="str">
         <f>D8&amp;"+"&amp;E8&amp;"+"&amp;F8&amp;"+"&amp;G8&amp;"+"&amp;H8&amp;"+"&amp;I8&amp;"+"&amp;J8&amp;"+"&amp;K8</f>
         <v>+++++++</v>
       </c>
     </row>
     <row r="10" spans="3:12">
-      <c r="C10" s="11"/>
-      <c r="D10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="9"/>
     </row>
     <row r="11" spans="3:12">
-      <c r="C11" s="10"/>
-      <c r="D11" s="13" t="str">
+      <c r="C11" s="9"/>
+      <c r="D11" s="12" t="str">
         <f>D10&amp;"+"&amp;E10&amp;"+"&amp;F10&amp;"+"&amp;G10&amp;"+"&amp;H10&amp;"+"&amp;I10&amp;"+"&amp;J10&amp;"+"&amp;K10</f>
         <v>+++++++</v>
       </c>
     </row>
     <row r="12" spans="3:12">
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
     </row>
     <row r="13" spans="3:12">
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
     </row>
     <row r="14" spans="3:12">
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -2001,9 +2068,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="C1:L14"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="1" width="23.625" customWidth="1"/>
+    <col min="1" max="1" width="23.6640625" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
   </cols>
@@ -2012,82 +2079,82 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="str">
+      <c r="D1" s="7" t="str">
         <f>"var code ="&amp;D3&amp;";"</f>
-        <v>var code =''is_click_sw('joystick_swVal') '+++++++;</v>
+        <v>var code =''is_click_sw()'+++++++;</v>
       </c>
     </row>
     <row r="2" spans="3:12">
-      <c r="C2" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="L2" s="18"/>
+      <c r="C2" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L2" s="17"/>
     </row>
     <row r="3" spans="3:12">
-      <c r="C3" s="10"/>
-      <c r="D3" s="13" t="str">
+      <c r="C3" s="9"/>
+      <c r="D3" s="12" t="str">
         <f>D2&amp;"+"&amp;E2&amp;"+"&amp;F2&amp;"+"&amp;G2&amp;"+"&amp;H2&amp;"+"&amp;I2&amp;"+"&amp;J2&amp;"+"&amp;K2</f>
-        <v>''is_click_sw('joystick_swVal') '+++++++</v>
+        <v>''is_click_sw()'+++++++</v>
       </c>
     </row>
     <row r="4" spans="3:12">
       <c r="C4" s="1"/>
-      <c r="D4" s="14"/>
+      <c r="D4" s="13"/>
     </row>
     <row r="5" spans="3:12">
-      <c r="C5" s="10"/>
-      <c r="D5" s="13" t="str">
+      <c r="C5" s="9"/>
+      <c r="D5" s="12" t="str">
         <f>D4&amp;"+"&amp;E4&amp;"+"&amp;F4&amp;"+"&amp;G4&amp;"+"&amp;H4&amp;"+"&amp;I4&amp;"+"&amp;J4&amp;"+"&amp;K4</f>
         <v>+++++++</v>
       </c>
     </row>
     <row r="6" spans="3:12">
-      <c r="C6" s="11"/>
-      <c r="D6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="9"/>
     </row>
     <row r="7" spans="3:12">
-      <c r="C7" s="10"/>
-      <c r="D7" s="13" t="str">
+      <c r="C7" s="9"/>
+      <c r="D7" s="12" t="str">
         <f>D6&amp;"+"&amp;E6&amp;"+"&amp;F6&amp;"+"&amp;G6&amp;"+"&amp;H6&amp;"+"&amp;I6&amp;"+"&amp;J6&amp;"+"&amp;K6</f>
         <v>+++++++</v>
       </c>
     </row>
     <row r="8" spans="3:12">
-      <c r="C8" s="11"/>
-      <c r="D8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="9"/>
     </row>
     <row r="9" spans="3:12">
-      <c r="C9" s="10"/>
-      <c r="D9" s="13" t="str">
+      <c r="C9" s="9"/>
+      <c r="D9" s="12" t="str">
         <f>D8&amp;"+"&amp;E8&amp;"+"&amp;F8&amp;"+"&amp;G8&amp;"+"&amp;H8&amp;"+"&amp;I8&amp;"+"&amp;J8&amp;"+"&amp;K8</f>
         <v>+++++++</v>
       </c>
     </row>
     <row r="10" spans="3:12">
-      <c r="C10" s="11"/>
-      <c r="D10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="9"/>
     </row>
     <row r="11" spans="3:12">
-      <c r="C11" s="10"/>
-      <c r="D11" s="13" t="str">
+      <c r="C11" s="9"/>
+      <c r="D11" s="12" t="str">
         <f>D10&amp;"+"&amp;E10&amp;"+"&amp;F10&amp;"+"&amp;G10&amp;"+"&amp;H10&amp;"+"&amp;I10&amp;"+"&amp;J10&amp;"+"&amp;K10</f>
         <v>+++++++</v>
       </c>
     </row>
     <row r="12" spans="3:12">
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
     </row>
     <row r="13" spans="3:12">
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
     </row>
     <row r="14" spans="3:12">
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
